--- a/matplotlib/employee.xlsx
+++ b/matplotlib/employee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dataanalysis-python\matplotlib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2C8F0C-24C8-43BB-8817-479ED86D7A80}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9522C6-52E3-4C65-BDDD-94F24EE5C2B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -465,13 +465,13 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.77734375" customWidth="1"/>
     <col min="9" max="9" width="18.33203125" customWidth="1"/>
   </cols>
@@ -890,7 +890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
@@ -913,7 +913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
@@ -936,7 +936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>36</v>
       </c>
